--- a/quote_forms/037_software_development_quote_request--quote_forms.xlsx
+++ b/quote_forms/037_software_development_quote_request--quote_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Open', 'value': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'In progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Cancelled', 'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'.net',_'value':_'.net'}</t>
+          <t>.net</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '.NET', 'value': '.net'}</t>
+          <t>.net</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'java',_'value':_'java'}</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Java', 'value': 'java'}</t>
+          <t>java</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'javascript',_'value':_'javascript'}</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'JavaScript', 'value': 'javascript'}</t>
+          <t>javascript</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
